--- a/business_surveys/012_rooftop_farming_survey--business_surveys.xlsx
+++ b/business_surveys/012_rooftop_farming_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1250,29 +1250,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>aquaponic</t>
+          <t>others</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Aquaponic</t>
+          <t>Others</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>rooftop_farm_types_choices</t>
+          <t>grower_employment_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>others</t>
+          <t>employed</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>Employed</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>employed</t>
+          <t>unemployed</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Employed</t>
+          <t>Unemployed</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>unemployed</t>
+          <t>retired</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Unemployed</t>
+          <t>Retired</t>
         </is>
       </c>
     </row>
@@ -1318,29 +1318,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>retired</t>
+          <t>self-employed</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Retired</t>
+          <t>Self-Employed</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>grower_employment_choices</t>
+          <t>grower_education_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>self-employed</t>
+          <t>high_school</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Self-Employed</t>
+          <t>High School</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>high_school</t>
+          <t>some_college</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>High School</t>
+          <t>Some College</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>some_college</t>
+          <t>bachelor's</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Some College</t>
+          <t>Bachelor's</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>bachelor's</t>
+          <t>post-graduate</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bachelor's</t>
+          <t>Post-Graduate</t>
         </is>
       </c>
     </row>
@@ -1403,29 +1403,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>post-graduate</t>
+          <t>others</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Post-Graduate</t>
+          <t>Others</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>grower_education_choices</t>
+          <t>grower_language_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>others</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>english</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>spanish</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spanish</t>
+          <t>French</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>french</t>
+          <t>german</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>French</t>
+          <t>German</t>
         </is>
       </c>
     </row>
@@ -1488,29 +1488,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>german</t>
+          <t>others</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>German</t>
+          <t>Others</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>grower_language_choices</t>
+          <t>grower_contact_method_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>others</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>mail</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Mail</t>
         </is>
       </c>
     </row>
@@ -1556,29 +1556,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>mail</t>
+          <t>others</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Mail</t>
+          <t>Others</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>grower_contact_method_choices</t>
+          <t>rooftop_farm_insurance_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>others</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1590,29 +1590,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>rooftop_farm_insurance_choices</t>
+          <t>rooftop_farm_equipment_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>water_pumps</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Water pumps</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>water_pumps</t>
+          <t>pumps_and_pipes</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Water pumps</t>
+          <t>Pumps and pipes</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>pumps_and_pipes</t>
+          <t>irrigation_system</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Pumps and pipes</t>
+          <t>Irrigation system</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>irrigation_system</t>
+          <t>greenhouse_or_hoophouse</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Irrigation system</t>
+          <t>Greenhouse or Hoophouse</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>greenhouse_or_hoophouse</t>
+          <t>tractors</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Greenhouse or Hoophouse</t>
+          <t>Tractors</t>
         </is>
       </c>
     </row>
@@ -1692,29 +1692,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>tractors</t>
+          <t>others</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tractors</t>
+          <t>Others</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>rooftop_farm_equipment_choices</t>
+          <t>rooftop_farming_certifications_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>others</t>
+          <t>usda</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>USDA</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>usda</t>
+          <t>organic_certification</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>USDA</t>
+          <t>Organic certification</t>
         </is>
       </c>
     </row>
@@ -1743,29 +1743,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>organic_certification</t>
+          <t>others</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Organic certification</t>
+          <t>Others</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>rooftop_farming_certifications_choices</t>
+          <t>farm_insurance_provider_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>others</t>
+          <t>company_a</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>Company A</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>company_a</t>
+          <t>company_b</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Company A</t>
+          <t>Company B</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>company_b</t>
+          <t>company_c</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Company B</t>
+          <t>Company C</t>
         </is>
       </c>
     </row>
@@ -1811,29 +1811,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>company_c</t>
+          <t>others</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Company C</t>
+          <t>Others</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>farm_insurance_provider_choices</t>
+          <t>farm_insurance_coverage_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>others</t>
+          <t>liability</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>Liability</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>liability</t>
+          <t>crop</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>Crop</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>crop</t>
+          <t>property</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Crop</t>
+          <t>Property</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>property</t>
+          <t>equipment</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Property</t>
+          <t>Equipment</t>
         </is>
       </c>
     </row>
@@ -1896,27 +1896,10 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>equipment</t>
+          <t>others</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
-        <is>
-          <t>Equipment</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>farm_insurance_coverage_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>others</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
         <is>
           <t>Others</t>
         </is>
